--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2022/4TO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXV/LTAIPT_A63F35A.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2022/4TO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXV/LTAIPT_A63F35A.xlsx
@@ -12,8 +12,10 @@
     <sheet name="Hidden_2" sheetId="3" r:id="rId3"/>
     <sheet name="Hidden_3" sheetId="4" r:id="rId4"/>
     <sheet name="Tabla_436729" sheetId="5" r:id="rId5"/>
+    <sheet name="Hidden_1_Tabla_436729" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
+    <definedName name="Hidden_1_Tabla_4367295">Hidden_1_Tabla_436729!$A$1:$A$2</definedName>
     <definedName name="Hidden_17">Hidden_1!$A$1:$A$4</definedName>
     <definedName name="Hidden_211">Hidden_2!$A$1:$A$2</definedName>
     <definedName name="Hidden_331">Hidden_3!$A$1:$A$7</definedName>
@@ -23,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="128">
   <si>
     <t>48996</t>
   </si>
@@ -299,34 +301,31 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>30C0E19A804F502B7A59C3A153F4CF23</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>01/10/2022</t>
-  </si>
-  <si>
-    <t>31/12/2022</t>
+    <t>7FD4A0CA8F289EEE38A1C3416BFAF337</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>01/01/2023</t>
+  </si>
+  <si>
+    <t>31/03/2023</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>4822666</t>
-  </si>
-  <si>
-    <t>Subdirección Jurídica.</t>
-  </si>
-  <si>
-    <t>12/01/2023</t>
-  </si>
-  <si>
-    <t>10/01/2023</t>
-  </si>
-  <si>
-    <t>Del periodo del 01 de octubre de 2022 al 31 de diciembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala no generó hipervínculo por toda vez que no hay una recomendación emitida por la Comisión Estatal de Derechos Humanos.</t>
+    <t>6271200</t>
+  </si>
+  <si>
+    <t>Subdirección Jurídica</t>
+  </si>
+  <si>
+    <t>24/04/2023</t>
+  </si>
+  <si>
+    <t>Del periodo del 01 de enero de 2023 al 31 de marzo de 2023, el Colegio de Bachilleres del Estado de Tlaxcala no generó hipervínculo por toda vez que no hay una recomendación emitida por la Comisión Estatal de Derechos Humanos.</t>
   </si>
   <si>
     <t>Recomendación específica</t>
@@ -377,6 +376,9 @@
     <t>56506</t>
   </si>
   <si>
+    <t>77790</t>
+  </si>
+  <si>
     <t>Id</t>
   </si>
   <si>
@@ -387,6 +389,27 @@
   </si>
   <si>
     <t>Segundo apellido</t>
+  </si>
+  <si>
+    <t>Sexo (catálogo)</t>
+  </si>
+  <si>
+    <t>F6E4E6B762F2A0299176A0914F244BF9</t>
+  </si>
+  <si>
+    <t>Óscal</t>
+  </si>
+  <si>
+    <t>Lobatón</t>
+  </si>
+  <si>
+    <t>Corona</t>
+  </si>
+  <si>
+    <t>Hombre</t>
+  </si>
+  <si>
+    <t>Mujer</t>
   </si>
 </sst>
 </file>
@@ -785,7 +808,7 @@
   <dimension ref="A1:AM8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.7109375" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="35.28515625" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
@@ -823,7 +846,7 @@
     <col min="36" max="36" width="73.140625" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="20" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="202" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="197.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" hidden="1" x14ac:dyDescent="0.25">
@@ -1367,10 +1390,10 @@
         <v>98</v>
       </c>
       <c r="AL8" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="AM8" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="AM8" s="3" t="s">
-        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -1384,13 +1407,13 @@
     <mergeCell ref="G3:I3"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H8:H200">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H8:H201">
       <formula1>Hidden_17</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="L8:L200">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="L8:L201">
       <formula1>Hidden_211</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AF8:AF200">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AF8:AF201">
       <formula1>Hidden_331</formula1>
     </dataValidation>
   </dataValidations>
@@ -1405,22 +1428,22 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -1435,12 +1458,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -1455,37 +1478,37 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -1495,15 +1518,18 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="C1" t="s">
         <v>6</v>
       </c>
@@ -1513,19 +1539,25 @@
       <c r="E1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D2" t="s">
         <v>114</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>115</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>117</v>
       </c>
@@ -1538,6 +1570,54 @@
       </c>
       <c r="E3" s="1" t="s">
         <v>120</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F4:F201">
+      <formula1>Hidden_1_Tabla_4367295</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>
